--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97654</v>
+        <v>97660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97660</v>
+        <v>97666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97666</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97669</v>
+        <v>97696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97696</v>
+        <v>97702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97723</v>
+        <v>97728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97728</v>
+        <v>97736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49083-2022 artfynd.xlsx
+++ b/artfynd/A 49083-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128610881</v>
       </c>
       <c r="B2" t="n">
-        <v>97736</v>
+        <v>98194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
